--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>6954</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.9103285770388795</v>
       </c>
     </row>
     <row r="7">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>7119</v>
+        <v>165</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.9319282628616311</v>
+        <v>0.02159968582275167</v>
       </c>
     </row>
     <row r="8">
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01714884147139678</v>
+        <v>0.007330802461055112</v>
       </c>
     </row>
     <row r="10">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>308</v>
+        <v>383</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.04031941353580312</v>
+        <v>0.05013745254614478</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15595,9 +15595,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15945,9 +15945,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -15980,9 +15980,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16225,9 +16225,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16295,9 +16295,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16435,9 +16435,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16505,9 +16505,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16540,9 +16540,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16575,9 +16575,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16645,9 +16645,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16680,9 +16680,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16715,9 +16715,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16750,9 +16750,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16820,9 +16820,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16925,9 +16925,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -16960,9 +16960,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17030,9 +17030,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17100,9 +17100,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17135,9 +17135,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17170,9 +17170,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17205,9 +17205,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17240,9 +17240,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17275,9 +17275,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17310,9 +17310,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17345,9 +17345,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17380,9 +17380,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17415,9 +17415,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17450,9 +17450,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17485,9 +17485,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17520,9 +17520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17555,9 +17555,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17590,9 +17590,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17660,9 +17660,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17695,9 +17695,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17730,9 +17730,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17765,9 +17765,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17800,9 +17800,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17835,9 +17835,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17870,9 +17870,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17905,9 +17905,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18208,9 +18208,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18593,9 +18593,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18733,9 +18733,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -18768,9 +18768,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19013,9 +19013,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19118,9 +19118,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19643,9 +19643,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -19853,9 +19853,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19923,9 +19923,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20098,9 +20098,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20343,9 +20343,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20518,9 +20518,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20658,9 +20658,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20693,9 +20693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20833,9 +20833,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20868,9 +20868,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -20903,9 +20903,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21043,9 +21043,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21113,9 +21113,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21148,9 +21148,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21218,9 +21218,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21253,9 +21253,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21288,9 +21288,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21428,9 +21428,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21526,7 +21526,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21941,9 +21941,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -21976,9 +21976,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22116,9 +22116,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22291,9 +22291,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22396,9 +22396,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22466,9 +22466,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22711,9 +22711,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22746,9 +22746,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22781,9 +22781,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22816,9 +22816,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22851,9 +22851,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22886,9 +22886,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -22921,9 +22921,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23026,9 +23026,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23096,9 +23096,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23131,9 +23131,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23166,9 +23166,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23201,9 +23201,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23236,9 +23236,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23271,9 +23271,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23306,9 +23306,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23341,9 +23341,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23376,9 +23376,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23411,9 +23411,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23446,9 +23446,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23481,9 +23481,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23516,9 +23516,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23551,9 +23551,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23586,9 +23586,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23621,9 +23621,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23656,9 +23656,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23691,9 +23691,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23726,9 +23726,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23761,9 +23761,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23796,9 +23796,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23831,9 +23831,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23866,9 +23866,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23901,9 +23901,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23936,9 +23936,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -23971,9 +23971,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24006,9 +24006,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24041,9 +24041,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24076,9 +24076,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24111,9 +24111,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24146,9 +24146,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24181,9 +24181,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24216,9 +24216,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24251,9 +24251,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24286,9 +24286,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24321,9 +24321,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24356,9 +24356,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24590,10 +24590,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>12299</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.7076117599677809</v>
       </c>
     </row>
     <row r="7">
@@ -24608,10 +24608,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13355</v>
+        <v>1056</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7683677578965538</v>
+        <v>0.0607559979287728</v>
       </c>
     </row>
     <row r="8">
@@ -24644,10 +24644,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1050</v>
+        <v>472</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06041079339508659</v>
+        <v>0.02715608998331511</v>
       </c>
     </row>
     <row r="10">
@@ -24662,10 +24662,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2394</v>
+        <v>2972</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1377366089407974</v>
+        <v>0.1709913123525689</v>
       </c>
     </row>
   </sheetData>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24743,10 +24743,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>11463</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.6101234830743028</v>
       </c>
     </row>
     <row r="7">
@@ -24761,10 +24761,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13043</v>
+        <v>1580</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.694219714711518</v>
+        <v>0.08409623163721525</v>
       </c>
     </row>
     <row r="8">
@@ -24797,10 +24797,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1683</v>
+        <v>799</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0895784543325527</v>
+        <v>0.04252714498616138</v>
       </c>
     </row>
     <row r="10">
@@ -24815,10 +24815,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2706</v>
+        <v>3590</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1440281030444965</v>
+        <v>0.1910794123908878</v>
       </c>
     </row>
   </sheetData>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38552,7 +38552,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38687,9 +38687,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -38757,9 +38757,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -38967,9 +38967,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39002,9 +39002,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39037,9 +39037,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -40157,9 +40157,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -40367,9 +40367,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40507,9 +40507,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40577,9 +40577,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40612,9 +40612,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40752,9 +40752,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40822,9 +40822,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40857,9 +40857,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40962,9 +40962,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -40997,9 +40997,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41032,9 +41032,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41067,9 +41067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41102,9 +41102,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41172,9 +41172,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41207,9 +41207,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41242,9 +41242,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41277,9 +41277,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41312,9 +41312,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41347,9 +41347,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41382,9 +41382,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41417,9 +41417,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41452,9 +41452,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41522,9 +41522,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41557,9 +41557,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41592,9 +41592,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41627,9 +41627,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42455,9 +42455,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42525,9 +42525,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42630,9 +42630,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42945,9 +42945,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43225,9 +43225,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43295,9 +43295,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43330,9 +43330,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43680,9 +43680,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43855,9 +43855,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44030,9 +44030,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44240,9 +44240,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44310,9 +44310,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44380,9 +44380,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44520,9 +44520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44835,9 +44835,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44975,9 +44975,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45045,9 +45045,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45150,9 +45150,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45248,7 +45248,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45873,9 +45873,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46713,9 +46713,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -47063,9 +47063,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47238,9 +47238,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47518,9 +47518,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47553,9 +47553,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47623,9 +47623,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47658,9 +47658,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47693,9 +47693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47798,9 +47798,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47938,9 +47938,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -47973,9 +47973,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48008,9 +48008,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48043,9 +48043,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48078,9 +48078,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -48113,9 +48113,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48148,9 +48148,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48183,9 +48183,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48218,9 +48218,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48253,9 +48253,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48288,9 +48288,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48323,9 +48323,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48557,10 +48557,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0</v>
+        <v>15144</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.7499628584162829</v>
       </c>
     </row>
     <row r="7">
@@ -48575,10 +48575,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>16176</v>
+        <v>1032</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.8010696776110533</v>
+        <v>0.05110681919477047</v>
       </c>
     </row>
     <row r="8">
@@ -48611,10 +48611,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>807</v>
+        <v>326</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03996434407963156</v>
+        <v>0.01614420838904571</v>
       </c>
     </row>
     <row r="10">
@@ -48629,10 +48629,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2946</v>
+        <v>3427</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.1458921408408854</v>
+        <v>0.1697122765314713</v>
       </c>
     </row>
   </sheetData>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65133,7 +65133,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65548,9 +65548,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -65653,9 +65653,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66038,9 +66038,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66248,9 +66248,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66773,9 +66773,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66878,9 +66878,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67088,9 +67088,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67193,9 +67193,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67228,9 +67228,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67263,9 +67263,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67298,9 +67298,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67333,9 +67333,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67368,9 +67368,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67473,9 +67473,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67613,9 +67613,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67648,9 +67648,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67718,9 +67718,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67823,9 +67823,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67858,9 +67858,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67893,9 +67893,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67928,9 +67928,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -67963,9 +67963,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68033,9 +68033,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68068,9 +68068,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68103,9 +68103,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68138,9 +68138,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68173,9 +68173,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68208,9 +68208,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68243,9 +68243,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68278,9 +68278,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68313,9 +68313,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68348,9 +68348,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68721,9 +68721,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68896,9 +68896,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69001,9 +69001,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69071,9 +69071,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69246,9 +69246,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69351,9 +69351,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69491,9 +69491,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69666,9 +69666,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69736,9 +69736,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69876,9 +69876,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69911,9 +69911,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69981,9 +69981,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70121,9 +70121,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70751,9 +70751,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70891,9 +70891,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70996,9 +70996,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71066,9 +71066,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71101,9 +71101,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71206,9 +71206,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71591,9 +71591,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71626,9 +71626,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71696,9 +71696,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71941,9 +71941,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71969,7 +71969,7 @@
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -72279,9 +72279,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72314,9 +72314,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73154,9 +73154,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73259,9 +73259,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -73294,9 +73294,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73399,9 +73399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73504,9 +73504,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -73644,9 +73644,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -73749,9 +73749,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -73784,9 +73784,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -73959,9 +73959,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73994,9 +73994,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74064,9 +74064,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74169,9 +74169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -74239,9 +74239,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74274,9 +74274,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74344,9 +74344,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74379,9 +74379,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74414,9 +74414,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74449,9 +74449,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74519,9 +74519,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74554,9 +74554,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74589,9 +74589,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74624,9 +74624,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74659,9 +74659,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74694,9 +74694,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74729,9 +74729,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74764,9 +74764,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74799,9 +74799,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74834,9 +74834,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74869,9 +74869,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74904,9 +74904,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74939,9 +74939,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -74974,9 +74974,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75009,9 +75009,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75079,9 +75079,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75219,9 +75219,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75254,9 +75254,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75289,9 +75289,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75324,9 +75324,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75359,9 +75359,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75429,9 +75429,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75464,9 +75464,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75499,9 +75499,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75534,9 +75534,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75569,9 +75569,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75604,9 +75604,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75639,9 +75639,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75674,9 +75674,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75709,9 +75709,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I110" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75744,9 +75744,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75849,9 +75849,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I114" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75884,9 +75884,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I115" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75919,9 +75919,9 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I116" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75954,9 +75954,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -75989,9 +75989,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+      <c r="I118" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80662,9 +80662,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -80700,9 +80700,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81004,9 +81004,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81156,9 +81156,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81194,9 +81194,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81422,9 +81422,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81460,9 +81460,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82334,9 +82334,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82448,9 +82448,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82638,9 +82638,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -83474,9 +83474,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84675,9 +84675,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84941,9 +84941,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85093,9 +85093,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85169,9 +85169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85207,9 +85207,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85397,9 +85397,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85701,9 +85701,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85777,9 +85777,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86233,9 +86233,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86309,9 +86309,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86955,9 +86955,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87259,9 +87259,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87373,9 +87373,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87411,9 +87411,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87639,9 +87639,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87677,9 +87677,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88095,9 +88095,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -89144,9 +89144,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89220,9 +89220,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89600,9 +89600,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91120,9 +91120,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91386,9 +91386,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91652,9 +91652,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24793,7 +24793,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -24811,7 +24811,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48607,7 +48607,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>$650-$1000</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -48625,7 +48625,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>≥$1500</t>
+          <t>≥$1000</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -852,11 +852,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -959,39 +959,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>56</v>
+        <v>439</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.007330802461055112</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>383</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.05013745254614478</v>
+        <v>0.0574682550071999</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6129,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10124,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14727,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14860,9 +14842,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15420,9 +15402,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15560,9 +15542,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17935,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18453,9 +18435,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20448,9 +20430,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20798,9 +20780,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21528,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22956,9 +22938,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23061,9 +23043,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24526,13 +24508,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24552,7 +24534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24633,39 +24615,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>472</v>
+        <v>3444</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.02715608998331511</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2972</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1709913123525689</v>
+        <v>0.198147402335884</v>
       </c>
     </row>
   </sheetData>
@@ -24679,11 +24643,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
@@ -24705,7 +24669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24786,39 +24750,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>799</v>
+        <v>4389</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.04252714498616138</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3590</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1910794123908878</v>
+        <v>0.2336065573770492</v>
       </c>
     </row>
   </sheetData>
@@ -24866,7 +24812,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33915,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38652,9 +38598,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39422,9 +39368,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39877,9 +39823,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39947,9 +39893,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -40332,9 +40278,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41755,9 +41701,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41860,9 +41806,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42035,9 +41981,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42105,9 +42051,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42140,9 +42086,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42175,9 +42121,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42245,9 +42191,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42280,9 +42226,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42385,9 +42331,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42560,9 +42506,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42700,9 +42646,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42735,9 +42681,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42770,9 +42716,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42875,9 +42821,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42910,9 +42856,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42980,9 +42926,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43120,9 +43066,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43155,9 +43101,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43190,9 +43136,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43260,9 +43206,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43470,9 +43416,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43505,9 +43451,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43575,9 +43521,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43715,9 +43661,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43785,9 +43731,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44275,9 +44221,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44345,9 +44291,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44555,9 +44501,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44590,9 +44536,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44940,9 +44886,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45010,9 +44956,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45185,9 +45131,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45214,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45348,9 +45294,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45418,9 +45364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45453,9 +45399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45488,9 +45434,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45558,9 +45504,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45593,9 +45539,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45663,9 +45609,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45803,9 +45749,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45978,9 +45924,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46048,9 +45994,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46258,9 +46204,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -47203,9 +47149,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48312,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48493,11 +48439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -48519,7 +48465,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48600,39 +48546,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1000</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>326</v>
+        <v>3753</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01614420838904571</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1000</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>3427</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1697122765314713</v>
+        <v>0.185856484920517</v>
       </c>
     </row>
   </sheetData>
@@ -48680,7 +48608,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53716,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57713,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60020,9 +59948,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="M46" s="12" t="n">
@@ -60550,7 +60478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65478,9 +65406,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -65863,9 +65791,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66703,9 +66631,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67578,9 +67506,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68756,9 +68684,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68791,9 +68719,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68861,9 +68789,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69036,9 +68964,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69106,9 +69034,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69316,9 +69244,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69456,9 +69384,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69526,9 +69454,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69561,9 +69489,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70016,9 +69944,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70296,9 +70224,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70366,9 +70294,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70436,9 +70364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70506,9 +70434,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70541,9 +70469,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70681,9 +70609,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71241,9 +71169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71486,9 +71414,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71836,9 +71764,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71917,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -72069,9 +71997,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72139,9 +72067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72174,9 +72102,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72349,9 +72277,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72594,9 +72522,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72629,9 +72557,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73889,9 +73817,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -75394,9 +75322,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -76040,7 +75968,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80464,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80966,9 +80894,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81384,9 +81312,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81916,9 +81844,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82068,9 +81996,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84903,9 +84831,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84979,9 +84907,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85245,9 +85173,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85283,9 +85211,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85359,9 +85287,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85587,9 +85515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85739,9 +85667,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85929,9 +85857,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86043,9 +85971,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86081,9 +86009,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86119,9 +86047,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86195,9 +86123,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86271,9 +86199,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86385,9 +86313,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86537,9 +86465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86727,9 +86655,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86765,9 +86693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87031,9 +86959,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87107,9 +87035,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87449,9 +87377,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87487,9 +87415,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87563,9 +87491,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87753,9 +87681,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87867,9 +87795,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88262,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88422,9 +88350,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88498,9 +88426,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88574,9 +88502,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88612,9 +88540,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88688,9 +88616,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88992,9 +88920,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89296,9 +89224,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89676,9 +89604,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89866,9 +89794,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90094,9 +90022,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90132,9 +90060,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90170,9 +90098,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90284,9 +90212,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90550,9 +90478,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90930,9 +90858,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91234,9 +91162,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91576,9 +91504,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24669,7 +24669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33915,7 +33915,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41621,7 +41621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45214,7 +45214,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48312,7 +48312,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48465,7 +48465,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53716,7 +53716,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57713,7 +57713,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60478,7 +60478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65081,7 +65081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68324,7 +68324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71917,7 +71917,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75968,7 +75968,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78575,7 +78575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80464,7 +80464,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84363,7 +84363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88262,7 +88262,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92158,7 +92158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21528,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24669,7 +24669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33915,7 +33915,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41621,7 +41621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45214,7 +45214,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48312,7 +48312,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48465,7 +48465,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48608,7 +48608,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53716,7 +53716,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57713,7 +57713,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60478,7 +60478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65081,7 +65081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68324,7 +68324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71917,7 +71917,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -75968,7 +75968,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78575,7 +78575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80464,7 +80464,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84363,7 +84363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88262,7 +88262,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92158,7 +92158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:53 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -852,11 +852,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -959,21 +959,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>439</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0574682550071999</v>
+        <v>0.01714884147139678</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.04031941353580312</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14842,9 +14860,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15402,9 +15420,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15542,9 +15560,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16487,9 +16505,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17327,9 +17345,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18190,9 +18208,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18435,9 +18453,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18750,9 +18768,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -18995,9 +19013,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19835,9 +19853,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20430,9 +20448,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -20780,9 +20798,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -21528,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22938,9 +22956,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -23043,9 +23061,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24508,13 +24526,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24534,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24615,21 +24633,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3444</v>
+        <v>1050</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.198147402335884</v>
+        <v>0.06041079339508659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2394</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.1377366089407974</v>
       </c>
     </row>
   </sheetData>
@@ -24643,11 +24679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
@@ -24669,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24750,21 +24786,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>4389</v>
+        <v>1683</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.2336065573770492</v>
+        <v>0.0895784543325527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2706</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.1440281030444965</v>
       </c>
     </row>
   </sheetData>
@@ -24812,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33915,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38598,9 +38652,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -38633,9 +38687,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -38703,9 +38757,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -38913,9 +38967,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -38948,9 +39002,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -38983,9 +39037,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -39368,9 +39422,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -39823,9 +39877,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -39893,9 +39947,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -40103,9 +40157,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -40278,9 +40332,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -41013,9 +41067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -41188,9 +41242,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -41621,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41701,9 +41755,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -41806,9 +41860,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -41981,9 +42035,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42051,9 +42105,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42086,9 +42140,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42121,9 +42175,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42191,9 +42245,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42226,9 +42280,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42331,9 +42385,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42401,9 +42455,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42471,9 +42525,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42506,9 +42560,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42576,9 +42630,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42646,9 +42700,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42681,9 +42735,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42716,9 +42770,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42821,9 +42875,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42856,9 +42910,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42891,9 +42945,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -42926,9 +42980,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43066,9 +43120,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43101,9 +43155,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43136,9 +43190,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43171,9 +43225,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43206,9 +43260,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43241,9 +43295,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43276,9 +43330,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43416,9 +43470,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43451,9 +43505,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43521,9 +43575,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43626,9 +43680,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43661,9 +43715,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43731,9 +43785,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43801,9 +43855,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -43976,9 +44030,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44186,9 +44240,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44221,9 +44275,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44256,9 +44310,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44291,9 +44345,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44326,9 +44380,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44466,9 +44520,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44501,9 +44555,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44536,9 +44590,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44781,9 +44835,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44886,9 +44940,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44921,9 +44975,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44956,9 +45010,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -44991,9 +45045,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45096,9 +45150,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45131,9 +45185,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45214,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45294,9 +45348,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45364,9 +45418,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45399,9 +45453,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45434,9 +45488,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45504,9 +45558,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45539,9 +45593,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45609,9 +45663,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45749,9 +45803,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45819,9 +45873,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45924,9 +45978,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -45994,9 +46048,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -46204,9 +46258,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -46659,9 +46713,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -47149,9 +47203,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -48024,9 +48078,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -48312,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48439,11 +48493,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -48465,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48546,21 +48600,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>≥$650</t>
+          <t>$650-$1500</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3753</v>
+        <v>807</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.185856484920517</v>
+        <v>0.03996434407963156</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥$1500</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2946</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.1458921408408854</v>
       </c>
     </row>
   </sheetData>
@@ -48608,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53716,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57713,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59948,9 +60020,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="M46" s="12" t="n">
@@ -60478,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65081,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65406,9 +65478,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -65476,9 +65548,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -65581,9 +65653,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -65791,9 +65863,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -65966,9 +66038,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -66176,9 +66248,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -66631,9 +66703,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -66701,9 +66773,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -67016,9 +67088,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -67156,9 +67228,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -67506,9 +67578,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68324,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68649,9 +68721,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68684,9 +68756,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68719,9 +68791,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68789,9 +68861,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68824,9 +68896,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68929,9 +69001,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68964,9 +69036,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -68999,9 +69071,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69034,9 +69106,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69174,9 +69246,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69244,9 +69316,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69279,9 +69351,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69384,9 +69456,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69419,9 +69491,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69454,9 +69526,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69489,9 +69561,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69594,9 +69666,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69664,9 +69736,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69804,9 +69876,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69839,9 +69911,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69909,9 +69981,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -69944,9 +70016,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70049,9 +70121,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70224,9 +70296,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70294,9 +70366,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70364,9 +70436,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70434,9 +70506,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70469,9 +70541,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70609,9 +70681,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70679,9 +70751,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70819,9 +70891,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70924,9 +70996,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -70994,9 +71066,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71029,9 +71101,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71134,9 +71206,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71169,9 +71241,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71414,9 +71486,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71519,9 +71591,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71554,9 +71626,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71624,9 +71696,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71764,9 +71836,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71869,9 +71941,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -71917,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71997,9 +72069,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72067,9 +72139,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72102,9 +72174,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72207,9 +72279,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72242,9 +72314,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72277,9 +72349,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72522,9 +72594,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -72557,9 +72629,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -73082,9 +73154,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -73222,9 +73294,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -73327,9 +73399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -73817,9 +73889,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -73887,9 +73959,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -74097,9 +74169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -75322,9 +75394,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -75968,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78575,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80464,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80590,9 +80662,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -80628,9 +80700,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -80894,9 +80966,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -80932,9 +81004,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81084,9 +81156,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81122,9 +81194,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81312,9 +81384,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81350,9 +81422,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81388,9 +81460,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81844,9 +81916,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -81996,9 +82068,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -82262,9 +82334,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -82376,9 +82448,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -82566,9 +82638,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -83402,9 +83474,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -84363,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84603,9 +84675,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -84831,9 +84903,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -84869,9 +84941,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -84907,9 +84979,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85021,9 +85093,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85097,9 +85169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85135,9 +85207,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85173,9 +85245,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85211,9 +85283,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85287,9 +85359,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85325,9 +85397,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85515,9 +85587,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85629,9 +85701,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85667,9 +85739,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85705,9 +85777,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85857,9 +85929,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -85971,9 +86043,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86009,9 +86081,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86047,9 +86119,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86123,9 +86195,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86161,9 +86233,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86199,9 +86271,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86237,9 +86309,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86313,9 +86385,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86465,9 +86537,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86655,9 +86727,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86693,9 +86765,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86883,9 +86955,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J70" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -86959,9 +87031,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J72" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87035,9 +87107,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87187,9 +87259,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87301,9 +87373,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87339,9 +87411,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87377,9 +87449,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87415,9 +87487,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87491,9 +87563,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87567,9 +87639,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87605,9 +87677,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87681,9 +87753,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -87795,9 +87867,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J94" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88023,9 +88095,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88262,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88350,9 +88422,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88426,9 +88498,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88502,9 +88574,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88540,9 +88612,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88616,9 +88688,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -88920,9 +88992,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89072,9 +89144,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89148,9 +89220,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89224,9 +89296,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89528,9 +89600,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89604,9 +89676,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -89794,9 +89866,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90022,9 +90094,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90060,9 +90132,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90098,9 +90170,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90212,9 +90284,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90478,9 +90550,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -90858,9 +90930,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J72" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -91048,9 +91120,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -91162,9 +91234,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -91314,9 +91386,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -91504,9 +91576,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J89" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -91580,9 +91652,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -92158,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -852,11 +852,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -959,39 +959,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>131</v>
+        <v>439</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.01714884147139678</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>308</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.04031941353580312</v>
+        <v>0.0574682550071999</v>
       </c>
     </row>
   </sheetData>
@@ -1039,7 +1021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6129,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10124,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14727,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14860,9 +14842,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15420,9 +15402,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15560,9 +15542,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16505,9 +16487,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17345,9 +17327,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17935,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18208,9 +18190,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18453,9 +18435,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -18768,9 +18750,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19013,9 +18995,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -19853,9 +19835,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20448,9 +20430,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -20798,9 +20780,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21528,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22956,9 +22938,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -23061,9 +23043,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24526,13 +24508,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24552,7 +24534,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24633,39 +24615,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1050</v>
+        <v>3444</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.06041079339508659</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2394</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1377366089407974</v>
+        <v>0.198147402335884</v>
       </c>
     </row>
   </sheetData>
@@ -24679,11 +24643,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
@@ -24705,7 +24669,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24786,39 +24750,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1683</v>
+        <v>4389</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.0895784543325527</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2706</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1440281030444965</v>
+        <v>0.2336065573770492</v>
       </c>
     </row>
   </sheetData>
@@ -24866,7 +24812,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29920,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33915,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38652,9 +38598,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -38687,9 +38633,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -38757,9 +38703,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -38967,9 +38913,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39002,9 +38948,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39037,9 +38983,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39422,9 +39368,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39877,9 +39823,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -39947,9 +39893,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -40157,9 +40103,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -40332,9 +40278,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41067,9 +41013,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41242,9 +41188,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41755,9 +41701,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -41860,9 +41806,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42035,9 +41981,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42105,9 +42051,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42140,9 +42086,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42175,9 +42121,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42245,9 +42191,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42280,9 +42226,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42385,9 +42331,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42455,9 +42401,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42525,9 +42471,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42560,9 +42506,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42630,9 +42576,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42700,9 +42646,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42735,9 +42681,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42770,9 +42716,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42875,9 +42821,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42910,9 +42856,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42945,9 +42891,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -42980,9 +42926,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43120,9 +43066,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43155,9 +43101,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43190,9 +43136,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43225,9 +43171,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43260,9 +43206,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43295,9 +43241,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43330,9 +43276,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43470,9 +43416,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43505,9 +43451,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43575,9 +43521,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43680,9 +43626,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43715,9 +43661,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43785,9 +43731,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -43855,9 +43801,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44030,9 +43976,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44240,9 +44186,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44275,9 +44221,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44310,9 +44256,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44345,9 +44291,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44380,9 +44326,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44520,9 +44466,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44555,9 +44501,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44590,9 +44536,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44835,9 +44781,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44940,9 +44886,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -44975,9 +44921,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45010,9 +44956,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45045,9 +44991,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45150,9 +45096,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45185,9 +45131,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45214,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45348,9 +45294,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45418,9 +45364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45453,9 +45399,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45488,9 +45434,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45558,9 +45504,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45593,9 +45539,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45663,9 +45609,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45803,9 +45749,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45873,9 +45819,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -45978,9 +45924,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46048,9 +45994,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46258,9 +46204,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -46713,9 +46659,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -47203,9 +47149,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -48078,9 +48024,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48312,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48493,11 +48439,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
@@ -48519,7 +48465,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48600,39 +48546,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>$650-$1500</t>
+          <t>≥$650</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>807</v>
+        <v>3753</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.03996434407963156</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥$1500</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>2946</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.1458921408408854</v>
+        <v>0.185856484920517</v>
       </c>
     </row>
   </sheetData>
@@ -48680,7 +48608,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53716,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57713,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60020,9 +59948,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="M46" s="12" t="n">
@@ -60550,7 +60478,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65478,9 +65406,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -65548,9 +65476,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -65653,9 +65581,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -65863,9 +65791,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66038,9 +65966,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66248,9 +66176,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66703,9 +66631,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -66773,9 +66701,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67088,9 +67016,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67228,9 +67156,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -67578,9 +67506,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68324,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68721,9 +68649,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68756,9 +68684,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68791,9 +68719,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68861,9 +68789,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -68896,9 +68824,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69001,9 +68929,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69036,9 +68964,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69071,9 +68999,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69106,9 +69034,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69246,9 +69174,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69316,9 +69244,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69351,9 +69279,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69456,9 +69384,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69491,9 +69419,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69526,9 +69454,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69561,9 +69489,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69666,9 +69594,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69736,9 +69664,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69876,9 +69804,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69911,9 +69839,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -69981,9 +69909,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70016,9 +69944,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70121,9 +70049,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70296,9 +70224,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70366,9 +70294,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70436,9 +70364,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70506,9 +70434,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70541,9 +70469,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70681,9 +70609,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70751,9 +70679,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70891,9 +70819,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -70996,9 +70924,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71066,9 +70994,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71101,9 +71029,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71206,9 +71134,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71241,9 +71169,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71486,9 +71414,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71591,9 +71519,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71626,9 +71554,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71696,9 +71624,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71836,9 +71764,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71941,9 +71869,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71917,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -72069,9 +71997,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72139,9 +72067,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72174,9 +72102,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72279,9 +72207,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72314,9 +72242,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72349,9 +72277,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72594,9 +72522,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -72629,9 +72557,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73154,9 +73082,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73294,9 +73222,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73399,9 +73327,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73889,9 +73817,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -73959,9 +73887,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -74169,9 +74097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -75394,9 +75322,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -76040,7 +75968,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80464,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80662,9 +80590,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -80700,9 +80628,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -80966,9 +80894,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81004,9 +80932,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81156,9 +81084,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81194,9 +81122,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81384,9 +81312,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81422,9 +81350,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81460,9 +81388,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -81916,9 +81844,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82068,9 +81996,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82334,9 +82262,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82448,9 +82376,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -82638,9 +82566,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -83474,9 +83402,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84675,9 +84603,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84903,9 +84831,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84941,9 +84869,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -84979,9 +84907,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85093,9 +85021,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85169,9 +85097,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85207,9 +85135,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85245,9 +85173,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85283,9 +85211,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85359,9 +85287,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85397,9 +85325,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85587,9 +85515,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85701,9 +85629,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85739,9 +85667,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85777,9 +85705,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -85929,9 +85857,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86043,9 +85971,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86081,9 +86009,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86119,9 +86047,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86195,9 +86123,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86233,9 +86161,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86271,9 +86199,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86309,9 +86237,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86385,9 +86313,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86537,9 +86465,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86727,9 +86655,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86765,9 +86693,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -86955,9 +86883,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87031,9 +86959,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87107,9 +87035,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87259,9 +87187,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87373,9 +87301,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87411,9 +87339,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87449,9 +87377,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87487,9 +87415,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87563,9 +87491,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87639,9 +87567,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87677,9 +87605,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87753,9 +87681,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -87867,9 +87795,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88095,9 +88023,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88262,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88422,9 +88350,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88498,9 +88426,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88574,9 +88502,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88612,9 +88540,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88688,9 +88616,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -88992,9 +88920,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89144,9 +89072,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89220,9 +89148,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89296,9 +89224,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89600,9 +89528,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89676,9 +89604,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -89866,9 +89794,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90094,9 +90022,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90132,9 +90060,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90170,9 +90098,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90284,9 +90212,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90550,9 +90478,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -90930,9 +90858,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91120,9 +91048,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91234,9 +91162,9 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91386,9 +91314,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91576,9 +91504,9 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -91652,9 +91580,9 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:52 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17953,7 +17953,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21546,7 +21546,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24399,7 +24399,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24552,7 +24552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24866,7 +24866,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29974,7 +29974,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33969,7 +33969,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -45268,7 +45268,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48519,7 +48519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48680,7 +48680,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -53788,7 +53788,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -57785,7 +57785,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -60550,7 +60550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -65153,7 +65153,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -68396,7 +68396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71989,7 +71989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -76040,7 +76040,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -78647,7 +78647,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -80536,7 +80536,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -84435,7 +84435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -88334,7 +88334,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -92230,7 +92230,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:54 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 21/05/2026 22:18 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 02:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 23/05/2026 22:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 03:40 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
+++ b/rates-nodispo/week-20/Analisis_Rates_NoDispo_7d.xlsx
@@ -572,7 +572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23725,7 +23725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23886,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32989,7 +32989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37592,7 +37592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40695,7 +40695,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47491,7 +47491,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47644,7 +47644,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47805,7 +47805,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -56910,7 +56910,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -59675,7 +59675,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -64278,7 +64278,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -67451,7 +67451,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -71044,7 +71044,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -74885,7 +74885,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -77492,7 +77492,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -79381,7 +79381,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -83128,7 +83128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -87027,7 +87027,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -90923,7 +90923,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
